--- a/data/Fall semester/Ni Analog Test Data.xlsx
+++ b/data/Fall semester/Ni Analog Test Data.xlsx
@@ -135,11 +135,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="848421046"/>
-        <c:axId val="982955009"/>
+        <c:axId val="418129167"/>
+        <c:axId val="789718224"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="848421046"/>
+        <c:axId val="418129167"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -191,10 +191,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="982955009"/>
+        <c:crossAx val="789718224"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="982955009"/>
+        <c:axId val="789718224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -269,7 +269,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="848421046"/>
+        <c:crossAx val="418129167"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
